--- a/00_Parks_4090000_NAReview_Tracker.xlsx
+++ b/00_Parks_4090000_NAReview_Tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tracker'!$1:$7</definedName>
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\-0.0%;\-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -105,6 +105,17 @@
       <family val="0"/>
       <b val="1"/>
       <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -204,7 +215,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -388,6 +399,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -642,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="31" min="1" max="1"/>
@@ -673,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1" s="32">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -1467,16 +1501,22 @@
           <t>$100k-1M</t>
         </is>
       </c>
-      <c r="I21" s="53" t="inlineStr">
-        <is>
-          <t>Queued</t>
-        </is>
-      </c>
-      <c r="J21" s="55" t="n"/>
-      <c r="K21" s="55" t="n">
+      <c r="I21" s="62" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J21" s="63" t="n">
         <v>236077.27</v>
       </c>
-      <c r="L21" s="54" t="n"/>
+      <c r="K21" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="64" t="inlineStr">
+        <is>
+          <t>Reviewed in full 11-Jun-2026: 114 lines reconcile to the 11-Jun SE2 to the cent at $236,378.27 (register basis); this row carries the 8-Jun SE2 actual $236,077.27, the $301.00 difference being the P12 Lockwise line 2908883 posted 8-Jun-2026 after the SE2 cut. Intake C00228240: 43 documents sighted, $157,051.42 (66.4%) evidenced. Findings F1-F7 held for ruling; no recode staged.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="32">
       <c r="A22" s="46" t="inlineStr">
@@ -2705,16 +2745,22 @@
           <t>$1k-10k</t>
         </is>
       </c>
-      <c r="I47" s="53" t="inlineStr">
-        <is>
-          <t>Queued</t>
-        </is>
-      </c>
-      <c r="J47" s="55" t="n"/>
-      <c r="K47" s="55" t="n">
-        <v>6032</v>
-      </c>
-      <c r="L47" s="54" t="n"/>
+      <c r="I47" s="62" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J47" s="63" t="n">
+        <v>2944</v>
+      </c>
+      <c r="K47" s="63" t="n">
+        <v>3088</v>
+      </c>
+      <c r="L47" s="64" t="inlineStr">
+        <is>
+          <t>Three internal journal lines on 1-20451 reviewed 11-Jun-2026 ($2,944.00); $16/unit rate validated from the Bega Road sheets; probable $1,232 IJ072723 duplicate held AMBER pending the full week's sheets. Remainder untested. Tax limb n/a (internal).</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="32">
       <c r="A48" s="46" t="inlineStr">
@@ -3189,16 +3235,22 @@
           <t>$1k-10k</t>
         </is>
       </c>
-      <c r="I57" s="53" t="inlineStr">
-        <is>
-          <t>Queued</t>
-        </is>
-      </c>
-      <c r="J57" s="55" t="n"/>
-      <c r="K57" s="55" t="n">
+      <c r="I57" s="62" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J57" s="63" t="n">
         <v>3682.5</v>
       </c>
-      <c r="L57" s="54" t="n"/>
+      <c r="K57" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="64" t="inlineStr">
+        <is>
+          <t>Full 3-line internal population reviewed 11-Jun-2026; register carries $7,570.50 including the P12 IJ074845 $3,888.00 posted 10-Jun-2026 after the 8-Jun SE2 cut (basis difference $3,888.00). IJ074028 $82.50 cleared on Tier 1; $7,488.00 oncharge backups unsighted. Tax limb n/a (internal).</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="32">
       <c r="A58" s="46" t="inlineStr">
@@ -3889,16 +3941,22 @@
           <t>&lt; $1k</t>
         </is>
       </c>
-      <c r="I72" s="47" t="inlineStr">
-        <is>
-          <t>Queued</t>
-        </is>
-      </c>
-      <c r="J72" s="49" t="n"/>
-      <c r="K72" s="49" t="n">
+      <c r="I72" s="65" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J72" s="66" t="n">
         <v>642.14</v>
       </c>
-      <c r="L72" s="48" t="n"/>
+      <c r="K72" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="67" t="inlineStr">
+        <is>
+          <t>Reviewed in full 11-Jun-2026: 6 lines net $642.14. TE004218 $6.05 parking miscode CLOSED (recoded to 73531 in-ledger via GJ078933, pair nets $0.00, direction correct); GJ075544 EOY pair nets out (FY25 Canungra advisory). Open: Trailbuilders TE004922 backup unsighted ($642.14 combined).</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="32">
       <c r="A73" s="52" t="inlineStr">
@@ -4942,6 +5000,48 @@
       <c r="K95" s="60">
         <f>SUM(K8:K94)</f>
         <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="68" t="inlineStr">
+        <is>
+          <t>Supplementary - outside the 87-account expense scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="69" t="inlineStr">
+        <is>
+          <t>SUPP</t>
+        </is>
+      </c>
+      <c r="B97" s="69" t="inlineStr">
+        <is>
+          <t>62121/62125</t>
+        </is>
+      </c>
+      <c r="C97" s="69" t="inlineStr">
+        <is>
+          <t>Cemetery Revenue (Garside query)</t>
+        </is>
+      </c>
+      <c r="H97" s="69" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="I97" s="69" t="inlineStr">
+        <is>
+          <t>Closed*</t>
+        </is>
+      </c>
+      <c r="J97" s="70" t="n">
+        <v>3711.73</v>
+      </c>
+      <c r="L97" s="71" t="inlineStr">
+        <is>
+          <t>Garside query reviewed 11-Jun-2026 (register row, $3,711.73): GJ076150 already reversed both PK000400 pre-purchase lines in-ledger; King five-document chain closed, nil GST errors. Residue: destination-leg confirmation (svc 20451) and burial invoices 505970/506368 unsighted. *Excluded from every KPI above (revenue account, not in the 87).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/00_Parks_4090000_NAReview_Tracker.xlsx
+++ b/00_Parks_4090000_NAReview_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="247">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  NA Review Programme Tracker</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t xml:space="preserve">Internal - Medical Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed 16-Jun-2026 (NA7B213 bundle). Whole-branch immunisation miscoded to NatAreas PK000432 via Internal_Medical.XLSM row 23; svc-PK split staged $3,799.50, 17 pairs, nets $0.00 (register export basis $4,861.70; SE2 $3,996.80). Coding/PK review complete; evidence all unsighted (GAP), SE2 not yet tied, off-branch $520.90 incl $146.30 duplicate to Finance. Overall AMBER.</t>
   </si>
   <si>
     <t xml:space="preserve">73140</t>
@@ -1134,15 +1137,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1513,7 +1516,7 @@
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="n">
         <f aca="false">COUNTIF(I8:I94,"Queued")</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="13" t="n">
@@ -3350,23 +3353,27 @@
         <v>32</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="J55" s="24"/>
+        <v>24</v>
+      </c>
+      <c r="J55" s="24" t="n">
+        <v>3996.8</v>
+      </c>
       <c r="K55" s="24" t="n">
-        <v>3996.8</v>
-      </c>
-      <c r="L55" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="23" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>3703.03</v>
@@ -3395,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3403,10 +3410,10 @@
         <v>117</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D57" s="24" t="n">
         <v>3682.5</v>
@@ -3435,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3443,10 +3450,10 @@
         <v>117</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>2068.21</v>
@@ -3473,7 +3480,7 @@
         <v>2068.21</v>
       </c>
       <c r="L58" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3481,10 +3488,10 @@
         <v>117</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D59" s="24" t="n">
         <v>1661.01</v>
@@ -3517,10 +3524,10 @@
         <v>117</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D60" s="18" t="n">
         <v>1643.76</v>
@@ -3553,10 +3560,10 @@
         <v>117</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D61" s="24" t="n">
         <v>1576.65</v>
@@ -3589,10 +3596,10 @@
         <v>117</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D62" s="18" t="n">
         <v>1313.28</v>
@@ -3625,10 +3632,10 @@
         <v>117</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D63" s="24" t="n">
         <v>1267.18</v>
@@ -3661,10 +3668,10 @@
         <v>117</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D64" s="18" t="n">
         <v>1246</v>
@@ -3697,10 +3704,10 @@
         <v>117</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D65" s="24" t="n">
         <v>1137.45</v>
@@ -3733,10 +3740,10 @@
         <v>117</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D66" s="18" t="n">
         <v>1098.04</v>
@@ -3769,10 +3776,10 @@
         <v>117</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D67" s="24" t="n">
         <v>1021.7</v>
@@ -3801,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3809,10 +3816,10 @@
         <v>117</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>938.18</v>
@@ -3829,7 +3836,7 @@
         <v>0.197320351468588</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I68" s="16" t="s">
         <v>38</v>
@@ -3845,10 +3852,10 @@
         <v>117</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D69" s="24" t="n">
         <v>908.99</v>
@@ -3865,7 +3872,7 @@
         <v/>
       </c>
       <c r="H69" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I69" s="22" t="s">
         <v>38</v>
@@ -3881,10 +3888,10 @@
         <v>117</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D70" s="18" t="n">
         <v>816.8</v>
@@ -3901,7 +3908,7 @@
         <v/>
       </c>
       <c r="H70" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I70" s="16" t="s">
         <v>38</v>
@@ -3917,10 +3924,10 @@
         <v>117</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D71" s="24" t="n">
         <v>704.79</v>
@@ -3937,7 +3944,7 @@
         <v/>
       </c>
       <c r="H71" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I71" s="22" t="s">
         <v>38</v>
@@ -3953,10 +3960,10 @@
         <v>117</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D72" s="18" t="n">
         <v>642.14</v>
@@ -3973,7 +3980,7 @@
         <v>0.923334531218847</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I72" s="30" t="s">
         <v>28</v>
@@ -3985,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3993,10 +4000,10 @@
         <v>117</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D73" s="24" t="n">
         <v>487.05</v>
@@ -4013,7 +4020,7 @@
         <v/>
       </c>
       <c r="H73" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I73" s="22" t="s">
         <v>38</v>
@@ -4029,10 +4036,10 @@
         <v>117</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D74" s="18" t="n">
         <v>426.79</v>
@@ -4049,7 +4056,7 @@
         <v/>
       </c>
       <c r="H74" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I74" s="16" t="s">
         <v>38</v>
@@ -4065,10 +4072,10 @@
         <v>117</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D75" s="24" t="n">
         <v>422.1</v>
@@ -4085,7 +4092,7 @@
         <v/>
       </c>
       <c r="H75" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I75" s="22" t="s">
         <v>38</v>
@@ -4101,10 +4108,10 @@
         <v>117</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D76" s="18" t="n">
         <v>384</v>
@@ -4121,7 +4128,7 @@
         <v/>
       </c>
       <c r="H76" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I76" s="16" t="s">
         <v>38</v>
@@ -4137,10 +4144,10 @@
         <v>117</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D77" s="24" t="n">
         <v>369.81</v>
@@ -4157,7 +4164,7 @@
         <v/>
       </c>
       <c r="H77" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>38</v>
@@ -4173,10 +4180,10 @@
         <v>117</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>337.58</v>
@@ -4193,7 +4200,7 @@
         <v/>
       </c>
       <c r="H78" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I78" s="16" t="s">
         <v>38</v>
@@ -4209,10 +4216,10 @@
         <v>117</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D79" s="24" t="n">
         <v>262.38</v>
@@ -4229,7 +4236,7 @@
         <v/>
       </c>
       <c r="H79" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I79" s="22" t="s">
         <v>38</v>
@@ -4245,10 +4252,10 @@
         <v>117</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>221.41</v>
@@ -4265,7 +4272,7 @@
         <v>0.915860716633669</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>38</v>
@@ -4281,10 +4288,10 @@
         <v>117</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D81" s="24" t="n">
         <v>207.89</v>
@@ -4301,7 +4308,7 @@
         <v/>
       </c>
       <c r="H81" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I81" s="22" t="s">
         <v>38</v>
@@ -4317,10 +4324,10 @@
         <v>117</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>159.42</v>
@@ -4337,7 +4344,7 @@
         <v/>
       </c>
       <c r="H82" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I82" s="16" t="s">
         <v>38</v>
@@ -4353,10 +4360,10 @@
         <v>117</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D83" s="24" t="n">
         <v>139.25</v>
@@ -4373,7 +4380,7 @@
         <v/>
       </c>
       <c r="H83" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I83" s="22" t="s">
         <v>28</v>
@@ -4385,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4393,10 +4400,10 @@
         <v>117</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>108.08</v>
@@ -4413,7 +4420,7 @@
         <v/>
       </c>
       <c r="H84" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I84" s="16" t="s">
         <v>38</v>
@@ -4429,10 +4436,10 @@
         <v>117</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D85" s="24" t="n">
         <v>88.14</v>
@@ -4449,7 +4456,7 @@
         <v/>
       </c>
       <c r="H85" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I85" s="22" t="s">
         <v>38</v>
@@ -4465,10 +4472,10 @@
         <v>117</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D86" s="18" t="n">
         <v>84.06</v>
@@ -4485,7 +4492,7 @@
         <v/>
       </c>
       <c r="H86" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I86" s="16" t="s">
         <v>38</v>
@@ -4501,10 +4508,10 @@
         <v>117</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D87" s="24" t="n">
         <v>14.56</v>
@@ -4521,7 +4528,7 @@
         <v/>
       </c>
       <c r="H87" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I87" s="22" t="s">
         <v>38</v>
@@ -4537,10 +4544,10 @@
         <v>117</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>0.36</v>
@@ -4557,7 +4564,7 @@
         <v/>
       </c>
       <c r="H88" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I88" s="16" t="s">
         <v>38</v>
@@ -4573,10 +4580,10 @@
         <v>117</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D89" s="24" t="n">
         <v>0</v>
@@ -4593,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I89" s="22" t="s">
         <v>38</v>
@@ -4607,10 +4614,10 @@
         <v>117</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D90" s="18" t="n">
         <v>0</v>
@@ -4627,7 +4634,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I90" s="16" t="s">
         <v>38</v>
@@ -4641,10 +4648,10 @@
         <v>117</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D91" s="24" t="n">
         <v>0</v>
@@ -4661,7 +4668,7 @@
         <v/>
       </c>
       <c r="H91" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I91" s="22" t="s">
         <v>38</v>
@@ -4675,10 +4682,10 @@
         <v>117</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D92" s="18" t="n">
         <v>0</v>
@@ -4695,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I92" s="16" t="s">
         <v>38</v>
@@ -4709,10 +4716,10 @@
         <v>117</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D93" s="24" t="n">
         <v>0</v>
@@ -4729,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I93" s="22" t="s">
         <v>38</v>
@@ -4743,10 +4750,10 @@
         <v>117</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>-11680</v>
@@ -4773,14 +4780,14 @@
         <v>-11680</v>
       </c>
       <c r="L94" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="33"/>
       <c r="B95" s="33"/>
       <c r="C95" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D95" s="35" t="n">
         <f aca="false">SUM(D8:D94)</f>
@@ -4799,39 +4806,39 @@
       <c r="I95" s="36"/>
       <c r="J95" s="35" t="n">
         <f aca="false">SUM(J8:J94)</f>
-        <v>493905.88</v>
+        <v>497902.68</v>
       </c>
       <c r="K95" s="35" t="n">
         <f aca="false">SUM(K8:K94)</f>
-        <v>33397704.28</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33393707.48</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C96" s="37" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B97" s="38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H97" s="38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I97" s="38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J97" s="39" t="n">
         <v>3711.73</v>
       </c>
       <c r="L97" s="40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4860,7 +4867,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9529AB4C-1E92-4D43-914A-6292DEAE9D60}</x14:id>
+          <x14:id>{EE853D80-F46B-419D-A821-413FF899D614}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4888,7 +4895,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9529AB4C-1E92-4D43-914A-6292DEAE9D60}">
+          <x14:cfRule type="dataBar" id="{EE853D80-F46B-419D-A821-413FF899D614}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/00_Parks_4090000_NAReview_Tracker.xlsx
+++ b/00_Parks_4090000_NAReview_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="237">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  NA Review Programme Tracker</t>
   </si>
@@ -226,7 +226,7 @@
     <t xml:space="preserve">Minor Contracts (below $20,000)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviewed in full 11-Jun-2026: 114 lines reconcile to the 11-Jun SE2 to the cent at $236,378.27 (register basis); this row carries the 8-Jun SE2 actual $236,077.27, the $301.00 difference being the P12 Lockwise line 2908883 posted 8-Jun-2026 after the SE2 cut. Intake C00228240: 43 documents sighted, $157,051.42 (66.4%) evidenced. Findings F1-F7 held for ruling; no recode staged.</t>
+    <t xml:space="preserve">Reviewed 11-Jun, evidence pass 17-Jun (88.3% sighted); AMBER, F1-F7 + candidates open. SE2 8-Jun basis $236,077.27; register SE2 reconciliation $236,378.27 (+$301 timing, post-8-Jun postings).</t>
   </si>
   <si>
     <t xml:space="preserve">7B114</t>
@@ -334,7 +334,7 @@
     <t xml:space="preserve">Garbage Collection</t>
   </si>
   <si>
-    <t xml:space="preserve">$22k actual vs $1.15M budget. Extreme under.</t>
+    <t xml:space="preserve">Reviewed 17-Jun (88% by line); coding correct, reconciles SE2 $0.00, NIL recode. AMBER on evidence: 4 of 9 Cleanaway months sighted, ABN not sighted.</t>
   </si>
   <si>
     <t xml:space="preserve">73609</t>
@@ -415,9 +415,6 @@
     <t xml:space="preserve">Internal - Spoils</t>
   </si>
   <si>
-    <t xml:space="preserve">Three internal journal lines on 1-20451 reviewed 11-Jun-2026 ($2,944.00); $16/unit rate validated from the Bega Road sheets; probable $1,232 IJ072723 duplicate held AMBER pending the full week's sheets. Remainder untested. Tax limb n/a (internal).</t>
-  </si>
-  <si>
     <t xml:space="preserve">73545</t>
   </si>
   <si>
@@ -478,7 +475,7 @@
     <t xml:space="preserve">Internal - Medical Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviewed 16-Jun-2026 (NA7B213 bundle). Whole-branch immunisation miscoded to NatAreas PK000432 via Internal_Medical.XLSM row 23; svc-PK split staged $3,799.50, 17 pairs, nets $0.00 (register export basis $4,861.70; SE2 $3,996.80). Coding/PK review complete; evidence all unsighted (GAP), SE2 not yet tied, off-branch $520.90 incl $146.30 duplicate to Finance. Overall AMBER.</t>
+    <t xml:space="preserve">17-Jun MERGE: whole-branch immunisation miscode; svc-PK split staged $3,799.50 nets $0.00 (export $4,861.70; SE2 $3,996.80). Evidence GAP; AMBER.</t>
   </si>
   <si>
     <t xml:space="preserve">73140</t>
@@ -496,9 +493,6 @@
     <t xml:space="preserve">Internal - Maintenance Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Full 3-line internal population reviewed 11-Jun-2026; register carries $7,570.50 including the P12 IJ074845 $3,888.00 posted 10-Jun-2026 after the 8-Jun SE2 cut (basis difference $3,888.00). IJ074028 $82.50 cleared on Tier 1; $7,488.00 oncharge backups unsighted. Tax limb n/a (internal).</t>
-  </si>
-  <si>
     <t xml:space="preserve">73127</t>
   </si>
   <si>
@@ -598,9 +592,6 @@
     <t xml:space="preserve">Conferences &amp; Seminar Fees</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviewed in full 11-Jun-2026: 6 lines net $642.14. TE004218 $6.05 parking miscode CLOSED (recoded to 73531 in-ledger via GJ078933, pair nets $0.00, direction correct); GJ075544 EOY pair nets out (FY25 Canungra advisory). Open: Trailbuilders TE004922 backup unsighted ($642.14 combined).</t>
-  </si>
-  <si>
     <t xml:space="preserve">73137</t>
   </si>
   <si>
@@ -743,41 +734,19 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplementary - outside the 87-account expense scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62121/62125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cemetery Revenue (Garside query)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garside query reviewed 11-Jun-2026 (register row, $3,711.73): GJ076150 already reversed both PK000400 pre-purchase lines in-ledger; King five-document chain closed, nil GST errors. Residue: destination-leg confirmation (svc 20451) and burial invoices 505970/506368 unsighted. *Excluded from every KPI above (revenue account, not in the 87).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;[RED]\-0.0%;\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,21 +826,6 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
       <name val="Segoe UI"/>
       <family val="0"/>
       <charset val="1"/>
@@ -988,169 +942,129 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1405,7 +1319,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -1506,17 +1420,17 @@
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="n">
         <f aca="false">SUMIF(I8:I94,"Closed",D8:D94)</f>
-        <v>375925.07</v>
+        <v>135523.16</v>
       </c>
       <c r="F6" s="10"/>
       <c r="G6" s="11" t="n">
         <f aca="false">SUMIF(I8:I94,"Partial",K8:K94)</f>
-        <v>7818368.62</v>
+        <v>7815280.62</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="n">
         <f aca="false">COUNTIF(I8:I94,"Queued")</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="13" t="n">
@@ -2082,16 +1996,16 @@
       <c r="H21" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="28" t="n">
+      <c r="I21" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="24" t="n">
         <v>236077.27</v>
       </c>
-      <c r="K21" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="29" t="s">
+      <c r="K21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="23" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2641,11 +2555,13 @@
         <v>23</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J36" s="18"/>
+        <v>24</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>21876.6</v>
+      </c>
       <c r="K36" s="18" t="n">
-        <v>21876.6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="17" t="s">
         <v>103</v>
@@ -3048,28 +2964,24 @@
       <c r="H47" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="28" t="n">
-        <v>2944</v>
-      </c>
-      <c r="K47" s="28" t="n">
-        <v>3088</v>
-      </c>
-      <c r="L47" s="29" t="s">
-        <v>130</v>
-      </c>
+      <c r="I47" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24" t="n">
+        <v>6032</v>
+      </c>
+      <c r="L47" s="23"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B48" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="17" t="s">
         <v>131</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>132</v>
       </c>
       <c r="D48" s="18" t="n">
         <v>5840.65</v>
@@ -3102,10 +3014,10 @@
         <v>117</v>
       </c>
       <c r="B49" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="23" t="s">
         <v>133</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>134</v>
       </c>
       <c r="D49" s="24" t="n">
         <v>5512.55</v>
@@ -3134,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3142,10 +3054,10 @@
         <v>117</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>136</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>137</v>
       </c>
       <c r="D50" s="18" t="n">
         <v>4739</v>
@@ -3165,7 +3077,7 @@
         <v>32</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J50" s="18" t="n">
         <v>4739</v>
@@ -3174,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3182,10 +3094,10 @@
         <v>117</v>
       </c>
       <c r="B51" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="23" t="s">
         <v>140</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>141</v>
       </c>
       <c r="D51" s="24" t="n">
         <v>4580.55</v>
@@ -3218,10 +3130,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>142</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>143</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>4267.49</v>
@@ -3250,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3258,10 +3170,10 @@
         <v>117</v>
       </c>
       <c r="B53" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>146</v>
       </c>
       <c r="D53" s="24" t="n">
         <v>4140.63</v>
@@ -3294,10 +3206,10 @@
         <v>117</v>
       </c>
       <c r="B54" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="17" t="s">
         <v>147</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>148</v>
       </c>
       <c r="D54" s="18" t="n">
         <v>4047.1</v>
@@ -3330,10 +3242,10 @@
         <v>117</v>
       </c>
       <c r="B55" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>150</v>
       </c>
       <c r="D55" s="24" t="n">
         <v>3996.8</v>
@@ -3362,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3370,10 +3282,10 @@
         <v>117</v>
       </c>
       <c r="B56" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" s="17" t="s">
         <v>152</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>153</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>3703.03</v>
@@ -3402,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3410,10 +3322,10 @@
         <v>117</v>
       </c>
       <c r="B57" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="23" t="s">
         <v>155</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>156</v>
       </c>
       <c r="D57" s="24" t="n">
         <v>3682.5</v>
@@ -3432,28 +3344,24 @@
       <c r="H57" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="I57" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="J57" s="28" t="n">
+      <c r="I57" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24" t="n">
         <v>3682.5</v>
       </c>
-      <c r="K57" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="29" t="s">
-        <v>157</v>
-      </c>
+      <c r="L57" s="23"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>2068.21</v>
@@ -3480,7 +3388,7 @@
         <v>2068.21</v>
       </c>
       <c r="L58" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3488,10 +3396,10 @@
         <v>117</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D59" s="24" t="n">
         <v>1661.01</v>
@@ -3524,10 +3432,10 @@
         <v>117</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D60" s="18" t="n">
         <v>1643.76</v>
@@ -3560,10 +3468,10 @@
         <v>117</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D61" s="24" t="n">
         <v>1576.65</v>
@@ -3596,10 +3504,10 @@
         <v>117</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D62" s="18" t="n">
         <v>1313.28</v>
@@ -3632,10 +3540,10 @@
         <v>117</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D63" s="24" t="n">
         <v>1267.18</v>
@@ -3668,10 +3576,10 @@
         <v>117</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D64" s="18" t="n">
         <v>1246</v>
@@ -3704,10 +3612,10 @@
         <v>117</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D65" s="24" t="n">
         <v>1137.45</v>
@@ -3740,10 +3648,10 @@
         <v>117</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D66" s="18" t="n">
         <v>1098.04</v>
@@ -3776,10 +3684,10 @@
         <v>117</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D67" s="24" t="n">
         <v>1021.7</v>
@@ -3808,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3816,10 +3724,10 @@
         <v>117</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>938.18</v>
@@ -3836,7 +3744,7 @@
         <v>0.197320351468588</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I68" s="16" t="s">
         <v>38</v>
@@ -3852,10 +3760,10 @@
         <v>117</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D69" s="24" t="n">
         <v>908.99</v>
@@ -3872,7 +3780,7 @@
         <v/>
       </c>
       <c r="H69" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I69" s="22" t="s">
         <v>38</v>
@@ -3888,10 +3796,10 @@
         <v>117</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D70" s="18" t="n">
         <v>816.8</v>
@@ -3908,7 +3816,7 @@
         <v/>
       </c>
       <c r="H70" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I70" s="16" t="s">
         <v>38</v>
@@ -3924,10 +3832,10 @@
         <v>117</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D71" s="24" t="n">
         <v>704.79</v>
@@ -3944,7 +3852,7 @@
         <v/>
       </c>
       <c r="H71" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I71" s="22" t="s">
         <v>38</v>
@@ -3960,10 +3868,10 @@
         <v>117</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D72" s="18" t="n">
         <v>642.14</v>
@@ -3980,30 +3888,26 @@
         <v>0.923334531218847</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="I72" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="J72" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18" t="n">
         <v>642.14</v>
       </c>
-      <c r="K72" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="32" t="s">
-        <v>191</v>
-      </c>
+      <c r="L72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D73" s="24" t="n">
         <v>487.05</v>
@@ -4020,7 +3924,7 @@
         <v/>
       </c>
       <c r="H73" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I73" s="22" t="s">
         <v>38</v>
@@ -4036,10 +3940,10 @@
         <v>117</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D74" s="18" t="n">
         <v>426.79</v>
@@ -4056,7 +3960,7 @@
         <v/>
       </c>
       <c r="H74" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I74" s="16" t="s">
         <v>38</v>
@@ -4072,10 +3976,10 @@
         <v>117</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D75" s="24" t="n">
         <v>422.1</v>
@@ -4092,7 +3996,7 @@
         <v/>
       </c>
       <c r="H75" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I75" s="22" t="s">
         <v>38</v>
@@ -4108,10 +4012,10 @@
         <v>117</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D76" s="18" t="n">
         <v>384</v>
@@ -4128,7 +4032,7 @@
         <v/>
       </c>
       <c r="H76" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I76" s="16" t="s">
         <v>38</v>
@@ -4144,10 +4048,10 @@
         <v>117</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D77" s="24" t="n">
         <v>369.81</v>
@@ -4164,7 +4068,7 @@
         <v/>
       </c>
       <c r="H77" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>38</v>
@@ -4180,10 +4084,10 @@
         <v>117</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>337.58</v>
@@ -4200,7 +4104,7 @@
         <v/>
       </c>
       <c r="H78" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I78" s="16" t="s">
         <v>38</v>
@@ -4216,10 +4120,10 @@
         <v>117</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D79" s="24" t="n">
         <v>262.38</v>
@@ -4236,7 +4140,7 @@
         <v/>
       </c>
       <c r="H79" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I79" s="22" t="s">
         <v>38</v>
@@ -4252,10 +4156,10 @@
         <v>117</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>221.41</v>
@@ -4272,7 +4176,7 @@
         <v>0.915860716633669</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>38</v>
@@ -4288,10 +4192,10 @@
         <v>117</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D81" s="24" t="n">
         <v>207.89</v>
@@ -4308,7 +4212,7 @@
         <v/>
       </c>
       <c r="H81" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I81" s="22" t="s">
         <v>38</v>
@@ -4324,10 +4228,10 @@
         <v>117</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>159.42</v>
@@ -4344,7 +4248,7 @@
         <v/>
       </c>
       <c r="H82" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I82" s="16" t="s">
         <v>38</v>
@@ -4360,10 +4264,10 @@
         <v>117</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D83" s="24" t="n">
         <v>139.25</v>
@@ -4380,7 +4284,7 @@
         <v/>
       </c>
       <c r="H83" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I83" s="22" t="s">
         <v>28</v>
@@ -4392,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4400,10 +4304,10 @@
         <v>117</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>108.08</v>
@@ -4420,7 +4324,7 @@
         <v/>
       </c>
       <c r="H84" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I84" s="16" t="s">
         <v>38</v>
@@ -4436,10 +4340,10 @@
         <v>117</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D85" s="24" t="n">
         <v>88.14</v>
@@ -4456,7 +4360,7 @@
         <v/>
       </c>
       <c r="H85" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I85" s="22" t="s">
         <v>38</v>
@@ -4472,10 +4376,10 @@
         <v>117</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D86" s="18" t="n">
         <v>84.06</v>
@@ -4492,7 +4396,7 @@
         <v/>
       </c>
       <c r="H86" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I86" s="16" t="s">
         <v>38</v>
@@ -4508,10 +4412,10 @@
         <v>117</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D87" s="24" t="n">
         <v>14.56</v>
@@ -4528,7 +4432,7 @@
         <v/>
       </c>
       <c r="H87" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I87" s="22" t="s">
         <v>38</v>
@@ -4544,10 +4448,10 @@
         <v>117</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>0.36</v>
@@ -4564,7 +4468,7 @@
         <v/>
       </c>
       <c r="H88" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I88" s="16" t="s">
         <v>38</v>
@@ -4580,10 +4484,10 @@
         <v>117</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D89" s="24" t="n">
         <v>0</v>
@@ -4600,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I89" s="22" t="s">
         <v>38</v>
@@ -4614,10 +4518,10 @@
         <v>117</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D90" s="18" t="n">
         <v>0</v>
@@ -4634,7 +4538,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I90" s="16" t="s">
         <v>38</v>
@@ -4648,10 +4552,10 @@
         <v>117</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D91" s="24" t="n">
         <v>0</v>
@@ -4668,7 +4572,7 @@
         <v/>
       </c>
       <c r="H91" s="23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I91" s="22" t="s">
         <v>38</v>
@@ -4682,10 +4586,10 @@
         <v>117</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D92" s="18" t="n">
         <v>0</v>
@@ -4702,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I92" s="16" t="s">
         <v>38</v>
@@ -4716,10 +4620,10 @@
         <v>117</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D93" s="24" t="n">
         <v>0</v>
@@ -4736,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I93" s="22" t="s">
         <v>38</v>
@@ -4750,10 +4654,10 @@
         <v>117</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>-11680</v>
@@ -4780,65 +4684,37 @@
         <v>-11680</v>
       </c>
       <c r="L94" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="33"/>
-      <c r="B95" s="33"/>
-      <c r="C95" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="D95" s="35" t="n">
+      <c r="A95" s="27"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D95" s="29" t="n">
         <f aca="false">SUM(D8:D94)</f>
         <v>33891610.16</v>
       </c>
-      <c r="E95" s="35" t="n">
+      <c r="E95" s="29" t="n">
         <f aca="false">SUM(E8:E94)</f>
         <v>40212294.73</v>
       </c>
-      <c r="F95" s="35" t="n">
+      <c r="F95" s="29" t="n">
         <f aca="false">SUM(F8:F94)</f>
         <v>6320684.57</v>
       </c>
-      <c r="G95" s="36"/>
-      <c r="H95" s="36"/>
-      <c r="I95" s="36"/>
-      <c r="J95" s="35" t="n">
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+      <c r="J95" s="29" t="n">
         <f aca="false">SUM(J8:J94)</f>
-        <v>497902.68</v>
-      </c>
-      <c r="K95" s="35" t="n">
+        <v>512510.64</v>
+      </c>
+      <c r="K95" s="29" t="n">
         <f aca="false">SUM(K8:K94)</f>
-        <v>33393707.48</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C96" s="37" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="B97" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="C97" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="H97" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="I97" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="J97" s="39" t="n">
-        <v>3711.73</v>
-      </c>
-      <c r="L97" s="40" t="s">
-        <v>246</v>
+        <v>33379099.52</v>
       </c>
     </row>
   </sheetData>
@@ -4867,7 +4743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EE853D80-F46B-419D-A821-413FF899D614}</x14:id>
+          <x14:id>{9556604A-47C5-491E-8D7E-1513C6DCE92C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4895,7 +4771,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EE853D80-F46B-419D-A821-413FF899D614}">
+          <x14:cfRule type="dataBar" id="{9556604A-47C5-491E-8D7E-1513C6DCE92C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
